--- a/RESULTS/tables/survival_logrank_external_risk_groups.xlsx
+++ b/RESULTS/tables/survival_logrank_external_risk_groups.xlsx
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2740.275769828596</v>
+        <v>2881.037024529517</v>
       </c>
       <c r="C2" t="n">
         <v>2</v>
